--- a/bench-no-docker/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
+++ b/bench-no-docker/ig/StructureDefinition-cds-bundle-response-recherche.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:51:56+00:00</t>
+    <t>2026-06-25T15:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
